--- a/data/trans_orig/IP11B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11B-Estudios-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41929</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52781</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65784</t>
+          <t>66495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>80,26%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94970</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18176</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>420</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
